--- a/artfynd/A 30241-2023 artfynd.xlsx
+++ b/artfynd/A 30241-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30241-2023 artfynd.xlsx
+++ b/artfynd/A 30241-2023 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>111215763</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30241-2023 artfynd.xlsx
+++ b/artfynd/A 30241-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111731932</v>
+        <v>111730046</v>
       </c>
       <c r="B17" t="n">
-        <v>89558</v>
+        <v>90666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2729,25 +2729,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>367444</v>
+        <v>367448</v>
       </c>
       <c r="R17" t="n">
         <v>6871417</v>
@@ -2794,27 +2794,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Växer under rötad silverved i kontinuitetskog</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111730046</v>
+        <v>111730403</v>
       </c>
       <c r="B18" t="n">
-        <v>90666</v>
+        <v>90709</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2864,25 +2859,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2899,10 +2894,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>367448</v>
+        <v>367510</v>
       </c>
       <c r="R18" t="n">
-        <v>6871417</v>
+        <v>6871297</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2934,7 +2929,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2944,7 +2939,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2982,10 +2977,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111730403</v>
+        <v>111730937</v>
       </c>
       <c r="B19" t="n">
-        <v>90709</v>
+        <v>88032</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2994,28 +2989,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5448</v>
+        <v>6276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3029,10 +3028,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>367510</v>
+        <v>367427</v>
       </c>
       <c r="R19" t="n">
-        <v>6871297</v>
+        <v>6871566</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3059,22 +3058,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3112,10 +3111,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111730937</v>
+        <v>111731274</v>
       </c>
       <c r="B20" t="n">
-        <v>88032</v>
+        <v>90666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3124,32 +3123,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3163,10 +3158,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>367427</v>
+        <v>367536</v>
       </c>
       <c r="R20" t="n">
-        <v>6871566</v>
+        <v>6871304</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3198,7 +3193,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3208,7 +3203,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3246,10 +3241,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111731274</v>
+        <v>111733035</v>
       </c>
       <c r="B21" t="n">
-        <v>90666</v>
+        <v>8377</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3262,30 +3257,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3293,10 +3290,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367536</v>
+        <v>367525</v>
       </c>
       <c r="R21" t="n">
-        <v>6871304</v>
+        <v>6871378</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3323,22 +3320,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3376,10 +3373,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111733035</v>
+        <v>111731060</v>
       </c>
       <c r="B22" t="n">
-        <v>8377</v>
+        <v>90709</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3388,36 +3385,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5448</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3425,10 +3416,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367525</v>
+        <v>367494</v>
       </c>
       <c r="R22" t="n">
-        <v>6871378</v>
+        <v>6871396</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3455,22 +3446,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3508,14 +3499,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111731060</v>
+        <v>111731030</v>
       </c>
       <c r="B23" t="n">
-        <v>90709</v>
+        <v>91628</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3524,21 +3515,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3551,10 +3542,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>367494</v>
+        <v>367473</v>
       </c>
       <c r="R23" t="n">
-        <v>6871396</v>
+        <v>6871475</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3586,7 +3577,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3596,7 +3587,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3634,41 +3625,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111731030</v>
+        <v>111730187</v>
       </c>
       <c r="B24" t="n">
-        <v>91628</v>
+        <v>90666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3677,10 +3672,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367473</v>
+        <v>367480</v>
       </c>
       <c r="R24" t="n">
-        <v>6871475</v>
+        <v>6871180</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3707,22 +3702,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3742,7 +3737,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Sandtallskog. Kontinuitetsskog</t>
+          <t>Sandtallskog. Kontinuietsskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3760,7 +3755,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111730187</v>
+        <v>111729509</v>
       </c>
       <c r="B25" t="n">
         <v>90666</v>
@@ -3807,10 +3802,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367480</v>
+        <v>367352</v>
       </c>
       <c r="R25" t="n">
-        <v>6871180</v>
+        <v>6871698</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3842,7 +3837,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3852,7 +3847,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3872,7 +3867,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Sandtallskog. Kontinuietsskog</t>
+          <t>Sandtallskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3890,7 +3885,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111729509</v>
+        <v>111730985</v>
       </c>
       <c r="B26" t="n">
         <v>90666</v>
@@ -3924,11 +3919,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3937,10 +3928,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367352</v>
+        <v>367354</v>
       </c>
       <c r="R26" t="n">
-        <v>6871698</v>
+        <v>6871659</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3967,22 +3958,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4020,10 +4011,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111730985</v>
+        <v>111732570</v>
       </c>
       <c r="B27" t="n">
-        <v>90666</v>
+        <v>78579</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4032,25 +4023,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4063,10 +4054,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367354</v>
+        <v>367471</v>
       </c>
       <c r="R27" t="n">
-        <v>6871659</v>
+        <v>6871339</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4093,22 +4084,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer på gammal sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4146,14 +4142,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111732570</v>
+        <v>111730457</v>
       </c>
       <c r="B28" t="n">
-        <v>78579</v>
+        <v>91599</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4162,25 +4158,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367471</v>
+        <v>367515</v>
       </c>
       <c r="R28" t="n">
-        <v>6871339</v>
+        <v>6871295</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4219,27 +4219,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växer på gammal sälg</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4277,37 +4272,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111730457</v>
+        <v>111731309</v>
       </c>
       <c r="B29" t="n">
-        <v>91599</v>
+        <v>90666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4324,10 +4319,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>367515</v>
+        <v>367501</v>
       </c>
       <c r="R29" t="n">
-        <v>6871295</v>
+        <v>6871294</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4354,22 +4349,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4407,10 +4402,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111731309</v>
+        <v>111732925</v>
       </c>
       <c r="B30" t="n">
-        <v>90666</v>
+        <v>78107</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4419,33 +4414,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -4454,10 +4445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>367501</v>
+        <v>367522</v>
       </c>
       <c r="R30" t="n">
-        <v>6871294</v>
+        <v>6871384</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4484,7 +4475,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4494,7 +4485,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4519,7 +4510,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Sandtallskog. Kontinuitetsskog</t>
+          <t>Sandtallskog. Kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4537,10 +4528,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111732925</v>
+        <v>111729321</v>
       </c>
       <c r="B31" t="n">
-        <v>78107</v>
+        <v>90709</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4553,25 +4544,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -4580,10 +4579,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>367522</v>
+        <v>367478</v>
       </c>
       <c r="R31" t="n">
-        <v>6871384</v>
+        <v>6871540</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4610,22 +4609,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4645,7 +4634,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Sandtallskog. Kontinuitetsskog.</t>
+          <t>Hedtasllskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4663,10 +4652,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111729321</v>
+        <v>111732650</v>
       </c>
       <c r="B32" t="n">
-        <v>90709</v>
+        <v>88489</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4679,33 +4668,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5448</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4714,10 +4695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>367478</v>
+        <v>367500</v>
       </c>
       <c r="R32" t="n">
-        <v>6871540</v>
+        <v>6871172</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4744,12 +4725,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växer under silverved</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4769,7 +4765,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Hedtasllskog. Kontinuitetsskog</t>
+          <t>Sandtallskog. Kontinuitetskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4787,10 +4783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111732650</v>
+        <v>111729694</v>
       </c>
       <c r="B33" t="n">
-        <v>88489</v>
+        <v>90666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4799,29 +4795,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>367500</v>
+        <v>367376</v>
       </c>
       <c r="R33" t="n">
-        <v>6871172</v>
+        <v>6871619</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4860,27 +4860,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växer under silverved</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4900,7 +4895,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Sandtallskog. Kontinuitetskog</t>
+          <t>Sandtallskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4918,7 +4913,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111729694</v>
+        <v>111730844</v>
       </c>
       <c r="B34" t="n">
         <v>90666</v>
@@ -4952,11 +4947,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4965,10 +4956,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>367376</v>
+        <v>367524</v>
       </c>
       <c r="R34" t="n">
-        <v>6871619</v>
+        <v>6871315</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5000,7 +4991,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5010,7 +5001,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5030,7 +5021,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Sandtallskog. Kontinuitetsskog</t>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5048,37 +5039,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111730844</v>
+        <v>111738813</v>
       </c>
       <c r="B35" t="n">
-        <v>90666</v>
+        <v>91599</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5087,17 +5078,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sydost om Jämtgäddtjärn, Vassbo  Idre, Dlr</t>
+          <t>Sydost om Jämngäddtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367524</v>
+        <v>367504</v>
       </c>
       <c r="R35" t="n">
-        <v>6871315</v>
+        <v>6871204</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5121,22 +5112,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5145,19 +5136,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5174,14 +5154,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111738813</v>
+        <v>112182353</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>77689</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5190,40 +5170,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sydost om Jämngäddtjärnen, Dlr</t>
+          <t>Vassbo, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>367504</v>
+        <v>367393</v>
       </c>
       <c r="R36" t="n">
-        <v>6871204</v>
+        <v>6871676</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5247,22 +5228,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>08:58</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>08:58</t>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5277,22 +5253,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112182353</v>
+        <v>112183621</v>
       </c>
       <c r="B37" t="n">
-        <v>77689</v>
+        <v>90865</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5301,25 +5277,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5333,10 +5309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367393</v>
+        <v>367464</v>
       </c>
       <c r="R37" t="n">
-        <v>6871676</v>
+        <v>6871198</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5363,12 +5339,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5400,10 +5376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112183621</v>
+        <v>112181975</v>
       </c>
       <c r="B38" t="n">
-        <v>90865</v>
+        <v>77787</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5412,25 +5388,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>967</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5444,10 +5420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367464</v>
+        <v>367461</v>
       </c>
       <c r="R38" t="n">
-        <v>6871198</v>
+        <v>6871559</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5474,12 +5450,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5511,10 +5487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112181975</v>
+        <v>112182668</v>
       </c>
       <c r="B39" t="n">
-        <v>77787</v>
+        <v>77092</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5527,21 +5503,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>967</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5555,10 +5531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>367461</v>
+        <v>367517</v>
       </c>
       <c r="R39" t="n">
-        <v>6871559</v>
+        <v>6871351</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5622,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112182668</v>
+        <v>112183627</v>
       </c>
       <c r="B40" t="n">
-        <v>77092</v>
+        <v>78753</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5638,21 +5614,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5666,10 +5642,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>367517</v>
+        <v>367480</v>
       </c>
       <c r="R40" t="n">
-        <v>6871351</v>
+        <v>6871337</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5696,12 +5672,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5730,117 +5706,6 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>112183627</v>
-      </c>
-      <c r="B41" t="n">
-        <v>78753</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Vassbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>367480</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6871337</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30241-2023 artfynd.xlsx
+++ b/artfynd/A 30241-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111182619</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -966,6 +976,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111200610</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1072,6 +1087,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181975</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1217,6 +1237,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111215825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1343,6 +1368,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111732650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1462,6 +1492,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730155</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1588,6 +1623,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111732570</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1694,6 +1734,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183627</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1815,6 +1860,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111731366</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1956,6 +2006,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111153887</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2081,6 +2136,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730216</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2202,6 +2262,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730258</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2327,6 +2392,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730457</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2437,6 +2507,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111738813</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2562,6 +2637,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111729422</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2696,6 +2776,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111729473</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2821,6 +2906,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111729509</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2946,6 +3036,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111729621</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3071,6 +3166,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111729694</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3196,6 +3296,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730046</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3321,6 +3426,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730187</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3442,6 +3552,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730480</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3563,6 +3678,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730844</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3684,6 +3804,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730985</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3805,6 +3930,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111731006</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3926,6 +4056,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111731021</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4051,6 +4186,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111731274</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4176,6 +4316,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111731309</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4282,6 +4427,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183621</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4401,6 +4551,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111729321</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4526,6 +4681,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730403</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4647,6 +4807,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111731060</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4768,6 +4933,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111731030</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4897,6 +5067,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730937</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5003,6 +5178,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182353</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5109,6 +5289,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182668</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5230,6 +5415,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111732925</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5375,6 +5565,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111215763</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5502,6 +5697,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111733035</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5647,6 +5847,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111729372</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5777,8 +5982,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111730525</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>